--- a/docs/ui-pulse-eight/KyPulse-Council.xlsx
+++ b/docs/ui-pulse-eight/KyPulse-Council.xlsx
@@ -58098,7 +58098,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"frontend": {"status": "pass", "evidence": "checks/r6-frontend.txt", "sha256": "162ef4c1fa6fe8b64d1c48905f540d565c7710698391d1258bf74c1d386c4aab", "raw_sha256": "162ef4c1fa6fe8b64d1c48905f540d565c7710698391d1258bf74c1d386c4aab"}, "make_ci": {"status": "pass", "evidence": "checks/r6-make_ci.txt", "sha256": "729ee44435ccc7f70dcdf092902bf1a5555560908b1f6175fd401ca46a5faeb4", "raw_sha256": "729ee44435ccc7f70dcdf092902bf1a5555560908b1f6175fd401ca46a5faeb4"}, "impeccable": {"status": "reported2pinned-style findings", "evidence": "checks/r6-impeccable.txt", "sha256": "6a2d1b9c8d8665e08c7471d8f987e29c784f4edb5a7f28595d84f431fa508429", "raw_sha256": "6a2d1b9c8d8665e08c7471d8f987e29c784f4edb5a7f28595d84f431fa508429"}, "nav_before": {"status": "failed-as-expected", "evidence": "checks/r6-nav_before.txt", "sha256": "c3c6a73799ad2034918aa7d6d9b1c9be1a2266f9a33ad9cd40ab1dd3ca2225d2", "raw_sha256": "c3c6a73799ad2034918aa7d6d9b1c9be1a2266f9a33ad9cd40ab1dd3ca2225d2"}, "browser": {"status": "running", "evidence": "/tmp/kypulse-r6-browser.log"}, "native": {"status": "pass-scoped", "evidence": "native-round6.json", "result": "15px strong-ink results; one navigation; fully visible selected Logs tab after route/deep link; no overflow."}}</t>
+          <t xml:space="preserve">{"frontend": {"status": "pass", "evidence": "checks/r6-frontend.txt", "sha256": "162ef4c1fa6fe8b64d1c48905f540d565c7710698391d1258bf74c1d386c4aab", "raw_sha256": "162ef4c1fa6fe8b64d1c48905f540d565c7710698391d1258bf74c1d386c4aab"}, "make_ci": {"status": "pass", "evidence": "checks/r6-make_ci.txt", "sha256": "729ee44435ccc7f70dcdf092902bf1a5555560908b1f6175fd401ca46a5faeb4", "raw_sha256": "729ee44435ccc7f70dcdf092902bf1a5555560908b1f6175fd401ca46a5faeb4"}, "impeccable": {"status": "reported2pinned-style findings", "evidence": "checks/r6-impeccable.txt", "sha256": "6a2d1b9c8d8665e08c7471d8f987e29c784f4edb5a7f28595d84f431fa508429", "raw_sha256": "6a2d1b9c8d8665e08c7471d8f987e29c784f4edb5a7f28595d84f431fa508429"}, "nav_before": {"status": "failed-as-expected", "evidence": "checks/r6-nav_before.txt", "sha256": "764590e7f6b91a5f34d6edbb6307b4e1f9a1dd35185a211cd29dcd7992db828c", "raw_sha256": "c3c6a73799ad2034918aa7d6d9b1c9be1a2266f9a33ad9cd40ab1dd3ca2225d2", "normalization": "ANSI escapes and trailing line whitespace removed; raw SHA256 retained."}, "browser": {"status": "running", "evidence": "/tmp/kypulse-r6-browser.log", "scoped_result": "Light-phone delayed-font regression and existing deep-link regression passed after the fix; full suite still running."}, "native": {"status": "pass-scoped", "evidence": "native-round6.json", "result": "15px strong-ink results; one navigation; fully visible selected Logs tab after route/deep link; no overflow."}}</t>
         </is>
       </c>
     </row>
